--- a/DocBusinessThienAn/BaoCao/BaoCaoTuan/PCN_WeeklyReport_20261019.xlsx
+++ b/DocBusinessThienAn/BaoCao/BaoCaoTuan/PCN_WeeklyReport_20261019.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30420" windowHeight="15860" tabRatio="348"/>
+    <workbookView windowWidth="30420" windowHeight="16380" tabRatio="348"/>
   </bookViews>
   <sheets>
     <sheet name="Weekly Report" sheetId="7" r:id="rId1"/>
@@ -267,10 +267,10 @@
     <t>ITS010</t>
   </si>
   <si>
-    <t>Phân hệ Chia sẻ Dữ liệu (ShareData - ESHARE):
+    <t xml:space="preserve">Phân hệ Chia sẻ Dữ liệu (ShareData - ESHARE):
 - Quản lý câu lệnh truy vấn mẫu và câu truy vấn tùy biến riêng theo từng đối tác; xây dựng cơ chế so sánh đối chiếu (Diff/Compare) trực quan hai phiên bản khi mẫu gốc thay đổi.
 - Chuẩn hóa quy trình phân tích cú pháp câu lệnh truy vấn để tự động trích xuất danh sách trường dữ liệu; xử lý đồng bộ các trường hợp lệch cột (thiếu trường, dư trường) giữa mẫu chung và mẫu riêng đối tác.
-- Tối ưu giao diện quản lý gói tin theo đối tác (thu gọn khung truy vấn, mở rộng danh sách trường, nhận diện trực quan nguồn mẫu chung / mẫu riêng) và hoàn thiện cơ chế khóa nối đuôi chuỗi kết hợp (@LastKey) chống trùng lặp mốc thời gian theo góp ý review của Tech Lead.</t>
+- Tối ưu giao diện quản lý gói tin theo đối tác (thu gọn khung truy vấn, mở rộng danh sách trường, nhận diện trực quan nguồn mẫu chung / mẫu riêng) và hoàn thiện cơ chế khóa nối đuôi chuỗi kết hợp (@LastKey) chống trùng lặp mốc thời gian theo góp ý review </t>
   </si>
   <si>
     <t>Đạt</t>
@@ -284,7 +284,7 @@
   </si>
   <si>
     <t>Phân hệ Chia sẻ Dữ liệu (ShareData):
-- Tiếp tục hoàn thiện và kiểm thử cơ chế quét dữ liệu nối đuôi nâng cao và các biến tham số hệ thống theo góp ý từ Tech Lead review.
+- Tiếp tục hoàn thiện và kiểm thử cơ chế quét dữ liệu nối đuôi nâng cao và các biến tham số hệ thống theo góp ý review.
 - Phối hợp kiểm thử tích hợp toàn trình luồng trích xuất dữ liệu động và gửi nhận với đối tác trên môi trường nội bộ.
 - Xây dựng và hoàn thiện tài liệu hướng dẫn cấu hình truy vấn động và nghiệm thu chức năng phân hệ.</t>
   </si>
@@ -533,6 +533,20 @@
       <charset val="134"/>
     </font>
     <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0000FF"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF002060"/>
@@ -542,20 +556,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF0000FF"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
@@ -2803,7 +2803,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7900F2B1-FFF1-4362-9EE7-8F2104ADA4E5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35BC5084-6A62-4303-AC36-7B5D2BD03084}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>
